--- a/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
+++ b/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9A6D18-D04C-4259-9DBB-3A5B615853A6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3ED78A-2630-40CA-9F2F-C527AFF5DC9D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19310" yWindow="170" windowWidth="18930" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19260" yWindow="50" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
   <si>
     <t>Name</t>
   </si>
@@ -51,9 +51,6 @@
     <t>Updated:01/23/21 by Tom Lever</t>
   </si>
   <si>
-    <t>Audio File (WAV)</t>
-  </si>
-  <si>
     <t>ChunkID</t>
   </si>
   <si>
@@ -96,24 +93,9 @@
     <t>data</t>
   </si>
   <si>
-    <t>Listening and Viewing App</t>
-  </si>
-  <si>
-    <t>A control to allow the Listening-and-Viewing-App Receiver to play / pause audio</t>
-  </si>
-  <si>
-    <t>A waveform graph of the audio corresponding to the processed audio or the request to listen and view</t>
-  </si>
-  <si>
-    <t>Annotations corresponding to rests and most-powerful pitches in the audio</t>
-  </si>
-  <si>
     <t>Outputs to Requester</t>
   </si>
   <si>
-    <t>Inputs from Requester other than Requests</t>
-  </si>
-  <si>
     <t>{'R', 'I', 'F', 'F'}</t>
   </si>
   <si>
@@ -157,6 +139,148 @@
   </si>
   <si>
     <t>Non-Data Bytes</t>
+  </si>
+  <si>
+    <t>Amalgamation</t>
+  </si>
+  <si>
+    <t>An audio signal</t>
+  </si>
+  <si>
+    <t>Rests and notes</t>
+  </si>
+  <si>
+    <t>Start times and durations of rests and notes</t>
+  </si>
+  <si>
+    <t>audio signal</t>
+  </si>
+  <si>
+    <t>Inputs from Requester</t>
+  </si>
+  <si>
+    <t>Use Case</t>
+  </si>
+  <si>
+    <t>Upload audio files</t>
+  </si>
+  <si>
+    <t>Signal of desire to upload and submit one or more audio files</t>
+  </si>
+  <si>
+    <t>Audio file (WAV)</t>
+  </si>
+  <si>
+    <t>Signal that each audio file should be uploaded by the system</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>Signal to abandon audio file</t>
+  </si>
+  <si>
+    <t>Mechanism to upload one or more audio files</t>
+  </si>
+  <si>
+    <t>Status of "successful upload"</t>
+  </si>
+  <si>
+    <t>"successful upload"</t>
+  </si>
+  <si>
+    <t>Status of "abandoned upload"</t>
+  </si>
+  <si>
+    <t>"abandoned upload"</t>
+  </si>
+  <si>
+    <t>Status of "failed upload"</t>
+  </si>
+  <si>
+    <t>"failed upload"</t>
+  </si>
+  <si>
+    <t>Process Uploaded Audio Files</t>
+  </si>
+  <si>
+    <t>Upload Audio files</t>
+  </si>
+  <si>
+    <t>Signal of desire to process one or more audio files</t>
+  </si>
+  <si>
+    <t>Selection of one or more audio files for processing</t>
+  </si>
+  <si>
+    <t>Signal to process audio files</t>
+  </si>
+  <si>
+    <t>Signal to abandon processing audio file</t>
+  </si>
+  <si>
+    <t>Set of all unprocessed uploaded audio files for which the Worker has permission to process</t>
+  </si>
+  <si>
+    <t>Status of "successful processing"</t>
+  </si>
+  <si>
+    <t>"successful processing"</t>
+  </si>
+  <si>
+    <t>Status of "abandoned processing"</t>
+  </si>
+  <si>
+    <t>"abandoned processing"</t>
+  </si>
+  <si>
+    <t>Status of "failed processing"</t>
+  </si>
+  <si>
+    <t>"failed processing"</t>
+  </si>
+  <si>
+    <t>Listen and View</t>
+  </si>
+  <si>
+    <t>Signal of desire to listen / view an amalgamation (see amalgamation in outputs)</t>
+  </si>
+  <si>
+    <t>rest</t>
+  </si>
+  <si>
+    <t>an region of an audio signal with small values relative to the signal's average value</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>a region of an audio signal with values that vary roughly sinusoidally and at the same frequency</t>
+  </si>
+  <si>
+    <t>start time</t>
+  </si>
+  <si>
+    <t>the product of the index of the first datum in a rest or note and the signal's sampling period</t>
+  </si>
+  <si>
+    <t>duration</t>
+  </si>
+  <si>
+    <t>the product of the difference between the first and last datum in a rest or note and
+the signal's sampling period</t>
+  </si>
+  <si>
+    <t>an array of 16-bit integers that represents music or speech</t>
+  </si>
+  <si>
+    <t>Request to listen to audio and view visualizations in an amalgation</t>
+  </si>
+  <si>
+    <t>Set of all amalgamations for which the Listener / Viewer has permission to listen / view</t>
+  </si>
+  <si>
+    <t>Requested amalgamation</t>
   </si>
 </sst>
 </file>
@@ -235,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -256,6 +380,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,344 +680,596 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E47"/>
+  <dimension ref="A2:E71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="54.6328125" customWidth="1"/>
+    <col min="3" max="3" width="81.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.81640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="19.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="19.5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B10" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B16" s="13"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B17" s="13"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B19" s="13"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="13"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B24" s="13"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B25" s="13"/>
+      <c r="C25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B26" s="13"/>
+      <c r="C26" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="13"/>
+      <c r="C28" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B29" s="13"/>
+      <c r="C29" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B30" s="13"/>
+      <c r="C30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C32" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="17"/>
+      <c r="C37" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="17"/>
+      <c r="C38" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="17"/>
+      <c r="C39" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="17"/>
+      <c r="C40" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="17"/>
+      <c r="C41" s="13"/>
+      <c r="D41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="17"/>
+      <c r="C42" s="13"/>
+      <c r="D42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="13"/>
+      <c r="C44" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="13"/>
+      <c r="C45" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="13"/>
+      <c r="C46" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="C48" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B52" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D52">
+        <v>4</v>
+      </c>
+      <c r="E52">
+        <f>SUM(D52:D65)</f>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B53" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B54" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B55" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D55">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B56" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D56">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B57" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B58" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="7">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="7">
+        <v>48000</v>
+      </c>
+      <c r="D59">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B60" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="7">
+        <v>16</v>
+      </c>
+      <c r="D60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B61" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B62" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B63" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B10" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B11" s="4"/>
-      <c r="C11" s="6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B12" s="4"/>
-      <c r="C12" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B13" s="4"/>
-      <c r="C13" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B14" s="5"/>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B15" s="5"/>
-      <c r="C15" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B16" s="5"/>
-      <c r="C16" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B17" s="5"/>
-      <c r="C17" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B18" s="5"/>
-      <c r="C18" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B19" s="5"/>
-      <c r="C19" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B20" s="5"/>
-      <c r="C20" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B21" s="5"/>
-      <c r="C21" s="8" t="s">
+      <c r="D63">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B64" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B65" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B22" s="5"/>
-      <c r="C22" s="8" t="s">
+      <c r="C65" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B66" s="8" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B23" s="5"/>
-      <c r="C23" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B26" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E32" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B33" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33">
-        <v>4</v>
-      </c>
-      <c r="E33">
-        <f>SUM(D33:D46)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B34" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B36" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B37" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D37">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B38" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B39" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C39" s="7">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B40" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" s="7">
-        <v>48000</v>
-      </c>
-      <c r="D40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B41" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="7">
-        <v>16</v>
-      </c>
-      <c r="D41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B42" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B43" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="7" t="s">
+      <c r="C66" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B44" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B45" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B46" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B47" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="C47" s="8" t="s">
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B67" t="s">
         <v>42</v>
       </c>
+      <c r="C67" s="16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B68" t="s">
+        <v>73</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B69" t="s">
+        <v>75</v>
+      </c>
+      <c r="C69" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B70" t="s">
+        <v>77</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>79</v>
+      </c>
+      <c r="C71" s="18" t="s">
+        <v>80</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B10:B23"/>
+  <mergeCells count="6">
+    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="C11:C24"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="B10:B26"/>
+    <mergeCell ref="B36:B42"/>
+    <mergeCell ref="B27:B30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
+++ b/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3ED78A-2630-40CA-9F2F-C527AFF5DC9D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C83EAD-4D28-4F3A-9536-9B579C8886D1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19260" yWindow="50" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19180" yWindow="0" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="88">
   <si>
     <t>Name</t>
   </si>
@@ -281,6 +281,15 @@
   </si>
   <si>
     <t>Requested amalgamation</t>
+  </si>
+  <si>
+    <t>Grant Permission</t>
+  </si>
+  <si>
+    <t>Signal of desire to process audio files or listen to / view an amalgamation</t>
+  </si>
+  <si>
+    <t>Permission to process audio files or listen to / view an amalgamation</t>
   </si>
 </sst>
 </file>
@@ -359,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -388,10 +397,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -680,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E71"/>
+  <dimension ref="A2:E73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
@@ -721,7 +734,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="18" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="15" t="s">
@@ -732,8 +745,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="13"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -741,98 +754,98 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="13"/>
-      <c r="C13" s="13"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
       <c r="D13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
       <c r="D14" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="13"/>
-      <c r="C15" s="14"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="13"/>
-      <c r="C16" s="14"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="13"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="19"/>
       <c r="D17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="13"/>
-      <c r="C18" s="14"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="13"/>
-      <c r="C20" s="14"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="13"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19"/>
       <c r="D21" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="13"/>
-      <c r="C22" s="14"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="19"/>
       <c r="D22" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="13"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
       <c r="D23" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="13"/>
-      <c r="C24" s="14"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="13"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="5" t="s">
         <v>48</v>
       </c>
@@ -841,7 +854,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="13"/>
+      <c r="B26" s="18"/>
       <c r="C26" s="5" t="s">
         <v>50</v>
       </c>
@@ -850,7 +863,7 @@
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -861,7 +874,7 @@
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="13"/>
+      <c r="B28" s="18"/>
       <c r="C28" s="5" t="s">
         <v>61</v>
       </c>
@@ -870,7 +883,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="13"/>
+      <c r="B29" s="18"/>
       <c r="C29" s="5" t="s">
         <v>62</v>
       </c>
@@ -879,7 +892,7 @@
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B30" s="13"/>
+      <c r="B30" s="18"/>
       <c r="C30" s="5" t="s">
         <v>63</v>
       </c>
@@ -888,7 +901,7 @@
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
+      <c r="B31" s="18" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -899,6 +912,7 @@
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" s="18"/>
       <c r="C32" s="5" t="s">
         <v>82</v>
       </c>
@@ -906,213 +920,214 @@
         <v>49</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="D36" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B36" s="17" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B37" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C37" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D36" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B37" s="17"/>
-      <c r="C37" s="15" t="s">
+      <c r="D37" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="20"/>
+      <c r="C38" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D38" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="17"/>
-      <c r="C38" s="15" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="20"/>
+      <c r="C39" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D39" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B39" s="17"/>
-      <c r="C39" s="15" t="s">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="20"/>
+      <c r="C40" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D40" s="15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B40" s="17"/>
-      <c r="C40" s="13" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="20"/>
+      <c r="C41" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="17"/>
-      <c r="C41" s="13"/>
-      <c r="D41" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="20"/>
+      <c r="C42" s="18"/>
+      <c r="D42" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="17"/>
-      <c r="C42" s="13"/>
-      <c r="D42" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="20"/>
+      <c r="C43" s="18"/>
+      <c r="D43" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B43" s="13" t="s">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C44" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D43" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B44" s="13"/>
-      <c r="C44" s="4" t="s">
+      <c r="D44" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="18"/>
+      <c r="C45" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B45" s="13"/>
-      <c r="C45" s="4" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="18"/>
+      <c r="C46" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B46" s="13"/>
-      <c r="C46" s="4" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="18"/>
+      <c r="C47" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B47" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C48" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C48" s="4" t="s">
+      <c r="D48" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B49" s="18"/>
+      <c r="C49" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
+      <c r="B50" t="s">
+        <v>85</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A52" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B51" s="3" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B53" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D53" t="s">
         <v>32</v>
       </c>
-      <c r="E51" t="s">
+      <c r="E53" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B52" s="9" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B54" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C54" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="D52">
-        <v>4</v>
-      </c>
-      <c r="E52">
-        <f>SUM(D52:D65)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B53" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B54" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
+      <c r="E54">
+        <f>SUM(D54:D67)</f>
+        <v>44</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B55" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>25</v>
+      <c r="B55" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="D55">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B56" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>26</v>
+      <c r="B56" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -1120,43 +1135,43 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B57" s="11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B58" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C58" s="7">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B59" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="7">
-        <v>48000</v>
+        <v>13</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B60" s="11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C60" s="7">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -1164,10 +1179,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B61" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="C61" s="7">
+        <v>48000</v>
       </c>
       <c r="D61">
         <v>4</v>
@@ -1175,101 +1190,125 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B62" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>30</v>
+        <v>18</v>
+      </c>
+      <c r="C62" s="7">
+        <v>16</v>
       </c>
       <c r="D62">
         <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B63" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C63" s="8" t="s">
-        <v>28</v>
+      <c r="B63" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D63">
         <v>4</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B64" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>35</v>
+      <c r="B64" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D64">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B65" s="8" t="s">
-        <v>20</v>
+      <c r="B65" s="12" t="s">
+        <v>19</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D65">
         <v>4</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B67" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B68" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="8" t="s">
+      <c r="C68" s="8" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B67" t="s">
-        <v>42</v>
-      </c>
-      <c r="C67" s="16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B68" t="s">
-        <v>73</v>
-      </c>
-      <c r="C68" s="16" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C70" s="16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
         <v>77</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C72" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="71" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B71" t="s">
+    <row r="73" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
         <v>79</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C73" s="17" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B43:B46"/>
+  <mergeCells count="8">
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B44:B47"/>
     <mergeCell ref="C11:C24"/>
-    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="C41:C43"/>
     <mergeCell ref="B10:B26"/>
-    <mergeCell ref="B36:B42"/>
+    <mergeCell ref="B37:B43"/>
     <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B31:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
+++ b/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C83EAD-4D28-4F3A-9536-9B579C8886D1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E69722C-4C5A-478C-9F49-7E927D7A69C0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19180" yWindow="0" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19180" yWindow="80" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
   <si>
     <t>Name</t>
   </si>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>Set of all amalgamations for which the Listener / Viewer has permission to listen / view</t>
-  </si>
-  <si>
-    <t>Requested amalgamation</t>
   </si>
   <si>
     <t>Grant Permission</t>
@@ -693,7 +690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E73"/>
+  <dimension ref="A2:E72"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
@@ -922,10 +919,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>85</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>86</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>49</v>
@@ -986,148 +983,150 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="20"/>
-      <c r="C41" s="18" t="s">
-        <v>38</v>
+      <c r="B41" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="20"/>
-      <c r="C42" s="18"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="4" t="s">
+        <v>65</v>
+      </c>
       <c r="D42" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B43" s="20"/>
-      <c r="C43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="D43" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B44" s="18" t="s">
-        <v>58</v>
-      </c>
+      <c r="B44" s="18"/>
       <c r="C44" s="4" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D44" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D45" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B45" s="18"/>
-      <c r="C45" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D45" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B46" s="18"/>
-      <c r="C46" s="4" t="s">
-        <v>67</v>
+      <c r="C46" s="18" t="s">
+        <v>38</v>
       </c>
       <c r="D46" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B47" s="18"/>
-      <c r="C47" s="4" t="s">
-        <v>69</v>
-      </c>
+      <c r="C47" s="18"/>
       <c r="D47" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B48" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>83</v>
-      </c>
+      <c r="B48" s="18"/>
+      <c r="C48" s="18"/>
       <c r="D48" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B49" s="18"/>
-      <c r="C49" s="4" t="s">
+      <c r="B49" t="s">
         <v>84</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="D49" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D50" t="s">
-        <v>49</v>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B53" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53">
         <v>4</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B53" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D53" t="s">
-        <v>32</v>
-      </c>
-      <c r="E53" t="s">
-        <v>37</v>
+      <c r="E53">
+        <f>SUM(D53:D66)</f>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B54" s="9" t="s">
-        <v>8</v>
+      <c r="B54" s="10" t="s">
+        <v>9</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54">
-        <f>SUM(D54:D67)</f>
-        <v>44</v>
-      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B55" s="10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D55">
         <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B56" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>24</v>
+      <c r="B56" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="D56">
         <v>4</v>
@@ -1135,10 +1134,10 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B57" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D57">
         <v>4</v>
@@ -1146,21 +1145,21 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B58" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B59" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>27</v>
+        <v>14</v>
+      </c>
+      <c r="C59" s="7">
+        <v>1</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -1168,147 +1167,136 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B60" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C60" s="7">
-        <v>1</v>
+        <v>48000</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B61" s="11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C61" s="7">
-        <v>48000</v>
+        <v>16</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B62" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" s="7">
         <v>16</v>
       </c>
+      <c r="C62" s="7" t="s">
+        <v>29</v>
+      </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B63" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B64" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D64">
         <v>4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B64" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D64">
-        <v>2</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B65" s="12" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B66" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D66">
         <v>4</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B66" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B67" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D67">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B68" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>36</v>
+      <c r="B68" t="s">
+        <v>42</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C69" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C71" s="16" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" ht="29" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>77</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B73" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C72" s="17" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B44:B47"/>
+    <mergeCell ref="B41:B44"/>
     <mergeCell ref="C11:C24"/>
-    <mergeCell ref="C41:C43"/>
     <mergeCell ref="B10:B26"/>
-    <mergeCell ref="B37:B43"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="B45:B48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
+++ b/Requester_and_Audio_Analyzer_System_Interface_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E69722C-4C5A-478C-9F49-7E927D7A69C0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3A38AC-7E2D-4B3E-99F0-304F00EFB9A7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19180" yWindow="80" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="100" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="91">
   <si>
     <t>Name</t>
   </si>
@@ -280,13 +280,25 @@
     <t>Set of all amalgamations for which the Listener / Viewer has permission to listen / view</t>
   </si>
   <si>
-    <t>Grant Permission</t>
-  </si>
-  <si>
-    <t>Signal of desire to process audio files or listen to / view an amalgamation</t>
-  </si>
-  <si>
-    <t>Permission to process audio files or listen to / view an amalgamation</t>
+    <t>Signal of desire to share</t>
+  </si>
+  <si>
+    <t>Designation of annotated audio files</t>
+  </si>
+  <si>
+    <t>Specification of receivers</t>
+  </si>
+  <si>
+    <t>Set of sharable annotated audio files</t>
+  </si>
+  <si>
+    <t>Notification of unidentifiable Receiver</t>
+  </si>
+  <si>
+    <t>Share Annotated Audio File</t>
+  </si>
+  <si>
+    <t>Annotated audio file(s)</t>
   </si>
 </sst>
 </file>
@@ -365,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -396,6 +408,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -690,7 +706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E72"/>
+  <dimension ref="A2:E76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
@@ -731,7 +747,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="20" t="s">
         <v>59</v>
       </c>
       <c r="C10" s="15" t="s">
@@ -742,8 +758,8 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="18"/>
-      <c r="C11" s="18" t="s">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20" t="s">
         <v>47</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -751,98 +767,98 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
+      <c r="B14" s="20"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="18"/>
-      <c r="C15" s="19"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21"/>
       <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="18"/>
-      <c r="C16" s="19"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="21"/>
       <c r="D16" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="18"/>
-      <c r="C17" s="19"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="21"/>
       <c r="D19" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="18"/>
-      <c r="C20" s="19"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="18"/>
-      <c r="C21" s="19"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="18"/>
-      <c r="C22" s="19"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
       <c r="D22" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="21"/>
       <c r="D23" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="18"/>
-      <c r="C24" s="19"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="21"/>
       <c r="D24" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="18"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="5" t="s">
         <v>48</v>
       </c>
@@ -851,7 +867,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="18"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="5" t="s">
         <v>50</v>
       </c>
@@ -860,7 +876,7 @@
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="20" t="s">
         <v>58</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -871,7 +887,7 @@
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="18"/>
+      <c r="B28" s="20"/>
       <c r="C28" s="5" t="s">
         <v>61</v>
       </c>
@@ -880,7 +896,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="18"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="5" t="s">
         <v>62</v>
       </c>
@@ -889,7 +905,7 @@
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B30" s="18"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="5" t="s">
         <v>63</v>
       </c>
@@ -898,7 +914,7 @@
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="20" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -909,7 +925,7 @@
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B32" s="18"/>
+      <c r="B32" s="20"/>
       <c r="C32" s="5" t="s">
         <v>82</v>
       </c>
@@ -918,259 +934,249 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
+      <c r="B33" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C33" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="D33" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="20"/>
+      <c r="C34" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="16" t="s">
+      <c r="D34" s="16" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
+      <c r="B35" s="20"/>
+      <c r="C35" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B36" s="3" t="s">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C38" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D38" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B37" s="20" t="s">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C39" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="20"/>
-      <c r="C38" s="15" t="s">
+      <c r="D39" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B40" s="22"/>
+      <c r="C40" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D40" s="15" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B39" s="20"/>
-      <c r="C39" s="15" t="s">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="22"/>
+      <c r="C41" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D41" s="15" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B40" s="20"/>
-      <c r="C40" s="15" t="s">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="22"/>
+      <c r="C42" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D42" s="15" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="18" t="s">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C43" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D41" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="18"/>
-      <c r="C42" s="4" t="s">
+      <c r="D43" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="20"/>
+      <c r="C44" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D44" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B43" s="18"/>
-      <c r="C43" s="4" t="s">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="20"/>
+      <c r="C45" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D45" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B44" s="18"/>
-      <c r="C44" s="4" t="s">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="20"/>
+      <c r="C46" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D46" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B45" s="18" t="s">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C47" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D45" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B46" s="18"/>
-      <c r="C46" s="18" t="s">
+      <c r="D47" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="20"/>
+      <c r="C48" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D48" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B47" s="18"/>
-      <c r="C47" s="18"/>
-      <c r="D47" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B49" s="20"/>
+      <c r="C49" s="20"/>
+      <c r="D49" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B48" s="18"/>
-      <c r="C48" s="18"/>
-      <c r="D48" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B50" s="20"/>
+      <c r="C50" s="20"/>
+      <c r="D50" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="D49" t="s">
-        <v>49</v>
-      </c>
-    </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
+      <c r="B51" t="s">
+        <v>89</v>
+      </c>
+      <c r="C51" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D51" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C52" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D52" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C53" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A55" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B52" s="3" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B56" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D56" t="s">
         <v>32</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E56" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B53" s="9" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B57" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C57" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="D53">
-        <v>4</v>
-      </c>
-      <c r="E53">
-        <f>SUM(D53:D66)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B54" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B55" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B56" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B57" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>26</v>
       </c>
       <c r="D57">
         <v>4</v>
       </c>
+      <c r="E57">
+        <f>SUM(D57:D70)</f>
+        <v>44</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B58" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>27</v>
+      <c r="B58" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B59" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C59" s="7">
-        <v>1</v>
+      <c r="B59" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B60" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60" s="7">
-        <v>48000</v>
+        <v>11</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>25</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -1178,125 +1184,170 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B61" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C61" s="7">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B62" s="11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B63" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>30</v>
+        <v>14</v>
+      </c>
+      <c r="C63" s="7">
+        <v>1</v>
       </c>
       <c r="D63">
         <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B64" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>28</v>
+      <c r="B64" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="7">
+        <v>48000</v>
       </c>
       <c r="D64">
         <v>4</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B65" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>35</v>
+      <c r="B65" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" s="7">
+        <v>16</v>
+      </c>
+      <c r="D65">
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B66" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="8" t="s">
-        <v>33</v>
+      <c r="B66" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="D66">
         <v>4</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B68" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B69" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B70" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B71" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C67" s="8" t="s">
+      <c r="C71" s="8" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B68" t="s">
+    <row r="72" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
         <v>42</v>
       </c>
-      <c r="C68" s="16" t="s">
+      <c r="C72" s="16" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B69" t="s">
+    <row r="73" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
         <v>73</v>
       </c>
-      <c r="C69" s="16" t="s">
+      <c r="C73" s="16" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B70" t="s">
+    <row r="74" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
         <v>75</v>
       </c>
-      <c r="C70" s="16" t="s">
+      <c r="C74" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B71" t="s">
+    <row r="75" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B75" t="s">
         <v>77</v>
       </c>
-      <c r="C71" s="16" t="s">
+      <c r="C75" s="16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="72" spans="2:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
+    <row r="76" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B76" t="s">
         <v>79</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C76" s="17" t="s">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B41:B44"/>
+  <mergeCells count="9">
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B43:B46"/>
     <mergeCell ref="C11:C24"/>
     <mergeCell ref="B10:B26"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="B45:B48"/>
+    <mergeCell ref="B39:B42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
